--- a/batchrapport-generator/Batchrapport_sjabloon.xlsx
+++ b/batchrapport-generator/Batchrapport_sjabloon.xlsx
@@ -12505,11 +12505,15 @@
       <c r="D74" s="1115" t="n"/>
       <c r="E74" s="1286" t="inlineStr">
         <is>
-          <t>Hoeveelheid</t>
+          <t>Ratio</t>
         </is>
       </c>
       <c r="F74" s="1114" t="n"/>
-      <c r="G74" s="1114" t="n"/>
+      <c r="G74" s="1114" t="inlineStr">
+        <is>
+          <t>Per brew</t>
+        </is>
+      </c>
       <c r="H74" s="1114" t="n"/>
       <c r="I74" s="1287" t="inlineStr">
         <is>
@@ -12923,11 +12927,15 @@
       <c r="D90" s="1115" t="n"/>
       <c r="E90" s="1286" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Ratio</t>
         </is>
       </c>
       <c r="F90" s="1114" t="n"/>
-      <c r="G90" s="1114" t="n"/>
+      <c r="G90" s="1114" t="inlineStr">
+        <is>
+          <t>Per batch</t>
+        </is>
+      </c>
       <c r="H90" s="1114" t="n"/>
       <c r="I90" s="1287" t="inlineStr">
         <is>
@@ -13525,8 +13533,10 @@
     <mergeCell ref="Q63:R63"/>
     <mergeCell ref="A60:D60"/>
     <mergeCell ref="A52:C52"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="G90:H90"/>
+    <mergeCell ref="E84:F84"/>
+    <mergeCell ref="G84:H84"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="L45:O45"/>
     <mergeCell ref="A49:C49"/>
@@ -13538,7 +13548,8 @@
     <mergeCell ref="A55:C55"/>
     <mergeCell ref="E48:F48"/>
     <mergeCell ref="G48:H48"/>
-    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="G77:H77"/>
     <mergeCell ref="I54:J54"/>
     <mergeCell ref="G12:J12"/>
     <mergeCell ref="A85:P85"/>
@@ -13554,7 +13565,8 @@
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A65:P65"/>
     <mergeCell ref="A76:D76"/>
-    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="G92:H92"/>
     <mergeCell ref="A78:D78"/>
     <mergeCell ref="I77:K77"/>
     <mergeCell ref="L59:O59"/>
@@ -13571,15 +13583,18 @@
     <mergeCell ref="L43:O43"/>
     <mergeCell ref="G13:J13"/>
     <mergeCell ref="G51:H51"/>
-    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="G80:H80"/>
     <mergeCell ref="I51:J51"/>
     <mergeCell ref="A91:D91"/>
     <mergeCell ref="G15:J15"/>
-    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="E82:F82"/>
+    <mergeCell ref="G82:H82"/>
     <mergeCell ref="I39:O39"/>
     <mergeCell ref="L84:P84"/>
     <mergeCell ref="E42:F42"/>
-    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="G83:H83"/>
     <mergeCell ref="L77:P77"/>
     <mergeCell ref="M66:P66"/>
     <mergeCell ref="A84:D84"/>
@@ -13669,18 +13684,21 @@
     <mergeCell ref="A64:D64"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="G63:I63"/>
-    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="E81:F81"/>
+    <mergeCell ref="G81:H81"/>
     <mergeCell ref="I42:J42"/>
     <mergeCell ref="K58:K63"/>
     <mergeCell ref="M70:P70"/>
-    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="G75:H75"/>
     <mergeCell ref="I52:J52"/>
     <mergeCell ref="I32:O32"/>
     <mergeCell ref="N40:O40"/>
     <mergeCell ref="I44:J44"/>
     <mergeCell ref="I66:L66"/>
     <mergeCell ref="K9:M9"/>
-    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="G76:H76"/>
     <mergeCell ref="I68:L68"/>
     <mergeCell ref="A62:D62"/>
     <mergeCell ref="R3:U14"/>
@@ -13703,7 +13721,8 @@
     <mergeCell ref="E58:F58"/>
     <mergeCell ref="N106:O106"/>
     <mergeCell ref="I45:J45"/>
-    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="G78:H78"/>
     <mergeCell ref="L80:P80"/>
     <mergeCell ref="I47:J47"/>
     <mergeCell ref="N23:P25"/>
@@ -13712,19 +13731,22 @@
     <mergeCell ref="G11:J11"/>
     <mergeCell ref="A5:D6"/>
     <mergeCell ref="L47:O47"/>
-    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="E94:F94"/>
+    <mergeCell ref="G94:H94"/>
     <mergeCell ref="A80:D80"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A82:D82"/>
     <mergeCell ref="A7:B8"/>
     <mergeCell ref="L58:O58"/>
-    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="G91:H91"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="L60:O60"/>
     <mergeCell ref="G64:J64"/>
     <mergeCell ref="A56:C56"/>
     <mergeCell ref="A27:C27"/>
-    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="G74:H74"/>
     <mergeCell ref="K3:M4"/>
     <mergeCell ref="G53:H53"/>
     <mergeCell ref="I53:J53"/>
@@ -13754,12 +13776,14 @@
     <mergeCell ref="G44:H44"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A3:B4"/>
-    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="E93:F93"/>
+    <mergeCell ref="G93:H93"/>
     <mergeCell ref="G20:J20"/>
     <mergeCell ref="G87:J87"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A106:C106"/>
-    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="E95:F95"/>
+    <mergeCell ref="G95:H95"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="G88:J88"/>
     <mergeCell ref="L91:P91"/>
@@ -13815,7 +13839,8 @@
     <mergeCell ref="A105:C105"/>
     <mergeCell ref="G61:I61"/>
     <mergeCell ref="G46:H46"/>
-    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="G79:H79"/>
     <mergeCell ref="L63:O63"/>
     <mergeCell ref="I71:L71"/>
     <mergeCell ref="E71:H71"/>

--- a/batchrapport-generator/Batchrapport_sjabloon.xlsx
+++ b/batchrapport-generator/Batchrapport_sjabloon.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recept-voorblad" sheetId="1" state="visible" r:id="rId1"/>
